--- a/i_test/test_D6_Table_2/g_output/D6_Table_2_caratterizzazione_coorte_sottopopolazione_CAP_other_combinations.xlsx
+++ b/i_test/test_D6_Table_2/g_output/D6_Table_2_caratterizzazione_coorte_sottopopolazione_CAP_other_combinations.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -518,307 +518,477 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>568</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>532</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>547</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>608</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>574</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BMI pregravidico basso (&lt;18,5), n (%)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>175 (29,7%)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>145 (26,7%)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>151 (27,0%)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>140 (26,5%)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>144 (25,9%)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>141 (25,4%)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>160 (27,6%)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>166 (28,1%)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>155 (31,0%)</t>
+          <t>Età alla data indice,</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BMI pregravidico medio (18,5-24,9), n (%)</t>
+          <t xml:space="preserve">  mediana (Q1 - Q3)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>190 (32,3%)</t>
+          <t>51 (41 - 62)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>185 (34,0%)</t>
+          <t>51 (41 - 60)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>194 (34,7%)</t>
+          <t>50 (39 - 61)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>181 (34,3%)</t>
+          <t>50 (39 - 59)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>198 (35,6%)</t>
+          <t>49 (39 - 60)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>197 (35,5%)</t>
+          <t>51 (41 - 61)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>190 (32,8%)</t>
+          <t>51 (41 - 61)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>204 (34,6%)</t>
+          <t>50 (40 - 60)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>159 (31,8%)</t>
+          <t>51 (42 - 61)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BMI pregravidico alto (&gt;24,9), n (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>224 (38,0%)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>214 (39,3%)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>214 (38,3%)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>207 (39,2%)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>214 (38,5%)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>217 (39,1%)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>229 (39,6%)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>220 (37,3%)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>186 (37,2%)</t>
+          <t>Classi età alla data indice</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diabete gestazionale, n (%)</t>
+          <t xml:space="preserve">  18-44, n (%)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>157 (26,7%)</t>
+          <t>189 (33,3%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>146 (26,8%)</t>
+          <t>188 (35,7%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>146 (26,1%)</t>
+          <t>198 (37,2%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>150 (28,4%)</t>
+          <t>214 (38,2%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>173 (31,1%)</t>
+          <t>210 (38,4%)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>138 (24,9%)</t>
+          <t>184 (34,5%)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>174 (30,1%)</t>
+          <t>180 (32,7%)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>181 (30,7%)</t>
+          <t>216 (35,5%)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>133 (26,6%)</t>
+          <t>196 (34,1%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  45-64, n (%)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>275 (48,4%)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>261 (49,5%)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>244 (45,9%)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>255 (45,5%)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>249 (45,5%)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>249 (46,7%)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>277 (50,3%)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>301 (49,5%)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>277 (48,3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BMI pregravidico basso (&lt;18,5), n (%)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>374 (65,8%)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>350 (66,4%)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>352 (66,2%)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>392 (70,0%)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>354 (64,7%)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>353 (66,2%)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>371 (67,3%)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>416 (68,4%)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>379 (66,0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BMI pregravidico medio (18,5-24,9), n (%)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>71 (12,5%)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>68 (12,9%)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>68 (12,8%)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>48 (8,6%)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>66 (12,1%)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>73 (13,7%)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>66 (12,0%)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>83 (13,7%)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>81 (14,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BMI pregravidico alto (&gt;24,9), n (%)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>123 (21,7%)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>109 (20,7%)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>112 (21,1%)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>120 (21,4%)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>127 (23,2%)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>107 (20,1%)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>114 (20,7%)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>109 (17,9%)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>114 (19,9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Diabete gestazionale, n (%)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>392 (69,0%)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>363 (68,9%)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>371 (69,7%)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>390 (69,6%)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>394 (72,0%)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>370 (69,4%)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>401 (72,8%)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>436 (71,7%)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>416 (72,5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Diabete pregravidico, n (%)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>443 (75,2%)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>380 (69,9%)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>402 (71,9%)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>394 (74,6%)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>410 (73,7%)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>413 (74,4%)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>410 (70,8%)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>430 (72,9%)</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>378 (75,6%)</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>376 (66,2%)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>361 (68,5%)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>366 (68,8%)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>379 (67,7%)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>358 (65,4%)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>366 (68,7%)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>396 (71,9%)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>370 (60,9%)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>372 (64,8%)</t>
         </is>
       </c>
     </row>
